--- a/output/pdf_financials_xlsx/TWR.xlsx
+++ b/output/pdf_financials_xlsx/TWR.xlsx
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.270296</v>
+        <v>-0.270296</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.244231</v>
+        <v>-0.244231</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.318975</v>
+        <v>-1.318975</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-0.533908</v>
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.270296</v>
+        <v>-0.270296</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.244231</v>
+        <v>-0.244231</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.318975</v>
+        <v>-1.318975</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.533908</v>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.270296</v>
+        <v>-0.270296</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.244231</v>
+        <v>-0.244231</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.318975</v>
+        <v>-1.318975</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-0.533908</v>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-43.965833</v>
+        <v>43.965833</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>26.6954</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.270296</v>
+        <v>-0.270296</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.244231</v>
+        <v>-0.244231</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.318975</v>
+        <v>-1.318975</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.533908</v>
@@ -2211,13 +2211,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.270296</v>
+        <v>-0.270296</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.244231</v>
+        <v>-0.244231</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.318975</v>
+        <v>-1.318975</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.530948</v>
@@ -2365,13 +2365,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -6094,49 +6094,49 @@
         <v>0.370674</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.373249</v>
+        <v>0.005721</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.493706</v>
+        <v>0.240524</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.698449</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.85594</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.6658269999999999</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.65765</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.427985</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.593943</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.618831</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.538046</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.715755</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.926166</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.183344</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.311913</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.653233</v>
       </c>
     </row>
     <row r="93">
@@ -7670,22 +7670,22 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.08287899999999999</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.126082</v>
+        <v>-1.604284</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.207495</v>
+        <v>-1.455687</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.735631</v>
+        <v>-0.008985</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.02389</v>
+        <v>-0.135206</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>2.542875</v>
+        <v>2.363687</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>-1.723572</v>
@@ -9958,7 +9958,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -11589,7 +11593,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -12157,7 +12165,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -27886,7 +27898,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -57648,16 +57664,16 @@
         </is>
       </c>
       <c r="E493" s="5" t="n">
-        <v>0.270296</v>
+        <v>-0.270296</v>
       </c>
       <c r="F493" s="5" t="n">
-        <v>0.244231</v>
+        <v>-0.244231</v>
       </c>
       <c r="G493" s="5" t="n">
-        <v>1.318975</v>
+        <v>-1.318975</v>
       </c>
       <c r="H493" s="5" t="n">
-        <v>0.419562</v>
+        <v>-0.419562</v>
       </c>
       <c r="I493" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TWR.xlsx
+++ b/output/pdf_financials_xlsx/TWR.xlsx
@@ -1077,28 +1077,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.067148</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000206</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002665</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.022885</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.025104</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.027509</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.006546</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.00181</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1107,19 +1107,19 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.006048</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.017966</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.001711</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.000749</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.00348</v>
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
@@ -2087,28 +2087,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.270296</v>
+        <v>-0.203148</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.244231</v>
+        <v>-0.244025</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.318975</v>
+        <v>-1.31631</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.533908</v>
+        <v>-0.556793</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.7873599999999999</v>
+        <v>-0.812464</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.308633</v>
+        <v>-0.336142</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.111349</v>
+        <v>-1.117895</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.328966</v>
+        <v>-0.330776</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-2.900243</v>
@@ -2117,19 +2117,19 @@
         <v>-0.6624409999999999</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.97263</v>
+        <v>-0.978678</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.686007</v>
+        <v>-0.703973</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.078207</v>
+        <v>-0.079918</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.352733</v>
+        <v>-0.353482</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.259935</v>
+        <v>-0.263415</v>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
@@ -2211,28 +2211,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.270296</v>
+        <v>-0.203148</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.244231</v>
+        <v>-0.244025</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.318975</v>
+        <v>-1.31631</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.530948</v>
+        <v>-0.553833</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.7708199999999999</v>
+        <v>-0.795924</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.287161</v>
+        <v>-0.31467</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.099109</v>
+        <v>-1.105655</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.320455</v>
+        <v>-0.322265</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-2.896198</v>
@@ -2241,19 +2241,19 @@
         <v>-0.656312</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.950709</v>
+        <v>-0.956757</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.668372</v>
+        <v>-0.686338</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.077829</v>
+        <v>-0.07954</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.352431</v>
+        <v>-0.35318</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.259694</v>
+        <v>-0.263174</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -2526,55 +2526,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.189263</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.014572</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.161864</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.058418</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.277454</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.852899</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.709013</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.378669</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.113121</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.4625</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.615376</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.121725</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.714714</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.369904</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.7237749999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.672044</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2.429561</v>
       </c>
     </row>
     <row r="35">
@@ -2642,55 +2642,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.189263</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.014572</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.161864</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.058418</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.277454</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.852899</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.709013</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.378669</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.113121</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.4625</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.615376</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.121725</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.0315</v>
+        <v>1.746214</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.005938</v>
+        <v>1.375842</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.010906</v>
+        <v>0.734681</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.021813</v>
+        <v>0.6938569999999999</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.03272</v>
+        <v>2.462281</v>
       </c>
     </row>
     <row r="37">
@@ -3338,55 +3338,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.291826</v>
+        <v>0.102563</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.088002</v>
+        <v>0.07343</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.18957</v>
+        <v>0.027706</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.060415</v>
+        <v>0.001997</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.302386</v>
+        <v>0.024932</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.867476</v>
+        <v>0.014577</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.731961</v>
+        <v>0.022948</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.39462</v>
+        <v>0.015951</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.121894</v>
+        <v>0.008773</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.484925</v>
+        <v>0.022425</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.64433</v>
+        <v>0.028954</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.129825</v>
+        <v>0.0081</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.73258</v>
+        <v>0.017866</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.389244</v>
+        <v>0.01934</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.732342</v>
+        <v>0.008567</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.6757570000000001</v>
+        <v>0.003713</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.504148</v>
+        <v>0.074587</v>
       </c>
     </row>
     <row r="49">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
@@ -49651,7 +49651,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -50348,7 +50348,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -51326,7 +51326,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -57462,7 +57462,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -58658,7 +58658,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E503" s="5" t="n">
